--- a/table/resources/sample/RouletteShop.xlsx
+++ b/table/resources/sample/RouletteShop.xlsx
@@ -113,16 +113,16 @@
     <t>list&lt;int&gt;{_}</t>
   </si>
   <si>
-    <t>Sequence</t>
+    <t>sequence</t>
   </si>
   <si>
     <t>item</t>
   </si>
   <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Frequency</t>
+    <t>purchase</t>
+  </si>
+  <si>
+    <t>frequency</t>
   </si>
   <si>
     <t>open</t>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>7</v>

--- a/table/resources/sample/RouletteShop.xlsx
+++ b/table/resources/sample/RouletteShop.xlsx
@@ -75,7 +75,7 @@
           </rPr>
           <t xml:space="preserve">
 1-开启
--1-不开启</t>
+0-不开启，可以不填</t>
         </r>
       </text>
     </comment>
@@ -110,7 +110,7 @@
     <t>int</t>
   </si>
   <si>
-    <t>list&lt;int&gt;{_}</t>
+    <t>map&lt;int{_}long&gt;{|}</t>
   </si>
   <si>
     <t>sequence</t>
@@ -1119,7 +1119,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="10.5" customWidth="1"/>
-    <col min="3" max="3" width="16.625" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="14.875" customWidth="1"/>
     <col min="5" max="5" width="16.125" customWidth="1"/>
     <col min="6" max="6" width="17.125" customWidth="1"/>
@@ -1324,9 +1324,7 @@
       <c r="F10" s="5">
         <v>10</v>
       </c>
-      <c r="G10" s="5">
-        <v>-1</v>
-      </c>
+      <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="4">
@@ -1345,9 +1343,7 @@
       <c r="F11" s="5">
         <v>10</v>
       </c>
-      <c r="G11" s="5">
-        <v>-1</v>
-      </c>
+      <c r="G11" s="5"/>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="4">
@@ -1366,9 +1362,7 @@
       <c r="F12" s="5">
         <v>10</v>
       </c>
-      <c r="G12" s="5">
-        <v>-1</v>
-      </c>
+      <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="4"/>

--- a/table/resources/sample/RouletteShop.xlsx
+++ b/table/resources/sample/RouletteShop.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="RouletteShop" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,30 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0">
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1. 财富轮盘商店
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -74,6 +97,28 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+-1表示不限次数	</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
 1-开启
 0-不开启，可以不填</t>
         </r>
@@ -84,11 +129,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
   <si>
     <t>id</t>
   </si>
   <si>
+    <t>商店类型</t>
+  </si>
+  <si>
     <t>商店表序列</t>
   </si>
   <si>
@@ -113,6 +161,9 @@
     <t>map&lt;int{_}long&gt;{|}</t>
   </si>
   <si>
+    <t>type</t>
+  </si>
+  <si>
     <t>sequence</t>
   </si>
   <si>
@@ -131,25 +182,55 @@
     <t>1022501_5</t>
   </si>
   <si>
+    <t>祈福卡</t>
+  </si>
+  <si>
     <t>1022502_1</t>
   </si>
   <si>
+    <t>刮刮卡</t>
+  </si>
+  <si>
     <t>1022503_2</t>
   </si>
   <si>
+    <t>夺宝优惠券</t>
+  </si>
+  <si>
     <t>1010301_1</t>
   </si>
   <si>
+    <t>赌场工具（普通）</t>
+  </si>
+  <si>
     <t>1010302_1</t>
   </si>
   <si>
+    <t>赌场工具（精良）</t>
+  </si>
+  <si>
     <t>1010303_1</t>
   </si>
   <si>
+    <t>赌场工具（优秀）</t>
+  </si>
+  <si>
     <t>1010304_1</t>
   </si>
   <si>
+    <t>赌场工具（绝佳）</t>
+  </si>
+  <si>
     <t>1010305_1</t>
+  </si>
+  <si>
+    <t>赌场工具（传奇）</t>
+  </si>
+  <si>
+    <t>1990000_30000</t>
+  </si>
+  <si>
+    <t>金币</t>
   </si>
 </sst>
 </file>
@@ -1115,25 +1196,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="2" width="10.5" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="14.875" customWidth="1"/>
-    <col min="5" max="5" width="16.125" customWidth="1"/>
-    <col min="6" max="6" width="17.125" customWidth="1"/>
-    <col min="7" max="7" width="11.375" customWidth="1"/>
-    <col min="8" max="8" width="17" customWidth="1"/>
-    <col min="15" max="15" width="10.375"/>
-    <col min="17" max="17" width="15.375" customWidth="1"/>
+    <col min="3" max="3" width="10.5" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="14.875" customWidth="1"/>
+    <col min="6" max="6" width="16.125" customWidth="1"/>
+    <col min="7" max="7" width="17.125" customWidth="1"/>
+    <col min="8" max="8" width="11.375" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="16" max="16" width="10.375"/>
+    <col min="18" max="18" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -1148,238 +1229,306 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2" t="s">
-        <v>7</v>
-      </c>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="D3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="G3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8">
       <c r="A4" s="4"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="5"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:8">
       <c r="A5" s="4">
-        <v>1</v>
-      </c>
-      <c r="B5" s="5">
-        <v>1</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5">
+        <f>B5*1000+C5</f>
+        <v>1001</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="5">
+        <v>5</v>
+      </c>
+      <c r="G5" s="5">
+        <v>2</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="4">
+        <f t="shared" ref="A6:A13" si="0">B6*1000+C6</f>
+        <v>1002</v>
+      </c>
+      <c r="B6" s="4">
+        <v>1</v>
+      </c>
+      <c r="C6" s="5">
+        <v>2</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="5">
+        <v>60</v>
+      </c>
+      <c r="G6" s="5">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="4">
+        <f t="shared" si="0"/>
+        <v>1003</v>
+      </c>
+      <c r="B7" s="4">
+        <v>1</v>
+      </c>
+      <c r="C7" s="5">
+        <v>3</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="5">
+        <v>100</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="4">
+        <f t="shared" si="0"/>
+        <v>1004</v>
+      </c>
+      <c r="B8" s="4">
+        <v>1</v>
+      </c>
+      <c r="C8" s="5">
+        <v>4</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="5">
         <v>10</v>
       </c>
-      <c r="F5" s="5">
+      <c r="G8" s="5">
         <v>10</v>
       </c>
-      <c r="G5" s="5">
+      <c r="H8" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="4">
+    <row r="9" spans="1:8">
+      <c r="A9" s="4">
+        <f t="shared" si="0"/>
+        <v>1005</v>
+      </c>
+      <c r="B9" s="4">
+        <v>1</v>
+      </c>
+      <c r="C9" s="5">
+        <v>5</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="5">
+        <v>20</v>
+      </c>
+      <c r="G9" s="5">
+        <v>5</v>
+      </c>
+      <c r="H9" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="4">
+        <f t="shared" si="0"/>
+        <v>1006</v>
+      </c>
+      <c r="B10" s="4">
+        <v>1</v>
+      </c>
+      <c r="C10" s="5">
+        <v>6</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="5">
+        <v>60</v>
+      </c>
+      <c r="G10" s="5">
         <v>2</v>
       </c>
-      <c r="B6" s="5">
-        <v>2</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5">
-        <v>20</v>
-      </c>
-      <c r="F6" s="5">
-        <v>10</v>
-      </c>
-      <c r="G6" s="5">
-        <v>1</v>
-      </c>
+      <c r="H10" s="5"/>
     </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="4">
-        <v>3</v>
-      </c>
-      <c r="B7" s="5">
-        <v>3</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5">
-        <v>6</v>
-      </c>
-      <c r="F7" s="5">
-        <v>10</v>
-      </c>
-      <c r="G7" s="5">
-        <v>1</v>
-      </c>
+    <row r="11" spans="1:8">
+      <c r="A11" s="4">
+        <f t="shared" si="0"/>
+        <v>1007</v>
+      </c>
+      <c r="B11" s="4">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5">
+        <v>7</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="5">
+        <v>80</v>
+      </c>
+      <c r="G11" s="5">
+        <v>1</v>
+      </c>
+      <c r="H11" s="5"/>
     </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="4">
-        <v>4</v>
-      </c>
-      <c r="B8" s="5">
-        <v>4</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5">
-        <v>2</v>
-      </c>
-      <c r="F8" s="5">
-        <v>50</v>
-      </c>
-      <c r="G8" s="5">
-        <v>1</v>
-      </c>
+    <row r="12" spans="1:8">
+      <c r="A12" s="4">
+        <f t="shared" si="0"/>
+        <v>1008</v>
+      </c>
+      <c r="B12" s="4">
+        <v>1</v>
+      </c>
+      <c r="C12" s="5">
+        <v>8</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="5">
+        <v>100</v>
+      </c>
+      <c r="G12" s="5">
+        <v>1</v>
+      </c>
+      <c r="H12" s="5"/>
     </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="4">
+    <row r="13" spans="1:8">
+      <c r="A13" s="4">
+        <f t="shared" si="0"/>
+        <v>1009</v>
+      </c>
+      <c r="B13" s="4">
+        <v>1</v>
+      </c>
+      <c r="C13" s="5">
+        <v>9</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="5">
         <v>5</v>
       </c>
-      <c r="B9" s="5">
-        <v>5</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5">
-        <v>3</v>
-      </c>
-      <c r="F9" s="5">
-        <v>50</v>
-      </c>
-      <c r="G9" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="4">
-        <v>6</v>
-      </c>
-      <c r="B10" s="5">
-        <v>6</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5">
-        <v>5</v>
-      </c>
-      <c r="F10" s="5">
-        <v>10</v>
-      </c>
-      <c r="G10" s="5"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="4">
-        <v>7</v>
-      </c>
-      <c r="B11" s="5">
-        <v>7</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5">
-        <v>8</v>
-      </c>
-      <c r="F11" s="5">
-        <v>10</v>
-      </c>
-      <c r="G11" s="5"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="4">
-        <v>8</v>
-      </c>
-      <c r="B12" s="5">
-        <v>8</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5">
-        <v>10</v>
-      </c>
-      <c r="F12" s="5">
-        <v>10</v>
-      </c>
-      <c r="G12" s="5"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="4"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="4"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="6"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
+      <c r="G13" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H13" s="5">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/table/resources/sample/RouletteShop.xlsx
+++ b/table/resources/sample/RouletteShop.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="RouletteShop" sheetId="1" r:id="rId1"/>
@@ -129,7 +129,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
   <si>
     <t>id</t>
   </si>
@@ -179,58 +179,22 @@
     <t>open</t>
   </si>
   <si>
-    <t>1022501_5</t>
-  </si>
-  <si>
-    <t>祈福卡</t>
-  </si>
-  <si>
-    <t>1022502_1</t>
-  </si>
-  <si>
-    <t>刮刮卡</t>
-  </si>
-  <si>
-    <t>1022503_2</t>
-  </si>
-  <si>
-    <t>夺宝优惠券</t>
-  </si>
-  <si>
-    <t>1010301_1</t>
-  </si>
-  <si>
-    <t>赌场工具（普通）</t>
-  </si>
-  <si>
-    <t>1010302_1</t>
-  </si>
-  <si>
-    <t>赌场工具（精良）</t>
-  </si>
-  <si>
-    <t>1010303_1</t>
-  </si>
-  <si>
-    <t>赌场工具（优秀）</t>
-  </si>
-  <si>
-    <t>1010304_1</t>
-  </si>
-  <si>
-    <t>赌场工具（绝佳）</t>
-  </si>
-  <si>
-    <t>1010305_1</t>
-  </si>
-  <si>
-    <t>赌场工具（传奇）</t>
-  </si>
-  <si>
-    <t>1990000_30000</t>
+    <t>1990000_3000</t>
   </si>
   <si>
     <t>金币</t>
+  </si>
+  <si>
+    <t>1990000_2000</t>
+  </si>
+  <si>
+    <t>1990000_1300</t>
+  </si>
+  <si>
+    <t>1990000_650</t>
+  </si>
+  <si>
+    <t>1990000_100</t>
   </si>
 </sst>
 </file>
@@ -402,12 +366,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1196,7 +1160,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="3" max="3" width="10.5" customWidth="1"/>
@@ -1307,14 +1271,15 @@
       <c r="D5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>17</v>
       </c>
       <c r="F5" s="5">
-        <v>5</v>
+        <f t="shared" ref="F5:F9" si="0">N9</f>
+        <v>0</v>
       </c>
       <c r="G5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" s="5">
         <v>1</v>
@@ -1322,7 +1287,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="4">
-        <f t="shared" ref="A6:A13" si="0">B6*1000+C6</f>
+        <f>B6*1000+C6</f>
         <v>1002</v>
       </c>
       <c r="B6" s="4">
@@ -1334,14 +1299,15 @@
       <c r="D6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>19</v>
+      <c r="E6" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="F6" s="5">
-        <v>60</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="G6" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" s="5">
         <v>1</v>
@@ -1349,7 +1315,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="4">
-        <f t="shared" si="0"/>
+        <f>B7*1000+C7</f>
         <v>1003</v>
       </c>
       <c r="B7" s="4">
@@ -1359,16 +1325,17 @@
         <v>3</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="F7" s="5">
-        <v>100</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="G7" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H7" s="5">
         <v>1</v>
@@ -1376,7 +1343,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="4">
-        <f t="shared" si="0"/>
+        <f>B8*1000+C8</f>
         <v>1004</v>
       </c>
       <c r="B8" s="4">
@@ -1386,16 +1353,17 @@
         <v>4</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="F8" s="5">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="G8" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H8" s="5">
         <v>1</v>
@@ -1403,7 +1371,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="4">
-        <f t="shared" si="0"/>
+        <f>B9*1000+C9</f>
         <v>1005</v>
       </c>
       <c r="B9" s="4">
@@ -1413,120 +1381,19 @@
         <v>5</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F9" s="5">
-        <v>20</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="G9" s="5">
         <v>5</v>
       </c>
       <c r="H9" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="4">
-        <f t="shared" si="0"/>
-        <v>1006</v>
-      </c>
-      <c r="B10" s="4">
-        <v>1</v>
-      </c>
-      <c r="C10" s="5">
-        <v>6</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="5">
-        <v>60</v>
-      </c>
-      <c r="G10" s="5">
-        <v>2</v>
-      </c>
-      <c r="H10" s="5"/>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="4">
-        <f t="shared" si="0"/>
-        <v>1007</v>
-      </c>
-      <c r="B11" s="4">
-        <v>1</v>
-      </c>
-      <c r="C11" s="5">
-        <v>7</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" s="5">
-        <v>80</v>
-      </c>
-      <c r="G11" s="5">
-        <v>1</v>
-      </c>
-      <c r="H11" s="5"/>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="4">
-        <f t="shared" si="0"/>
-        <v>1008</v>
-      </c>
-      <c r="B12" s="4">
-        <v>1</v>
-      </c>
-      <c r="C12" s="5">
-        <v>8</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="5">
-        <v>100</v>
-      </c>
-      <c r="G12" s="5">
-        <v>1</v>
-      </c>
-      <c r="H12" s="5"/>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="4">
-        <f t="shared" si="0"/>
-        <v>1009</v>
-      </c>
-      <c r="B13" s="4">
-        <v>1</v>
-      </c>
-      <c r="C13" s="5">
-        <v>9</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13" s="5">
-        <v>5</v>
-      </c>
-      <c r="G13" s="5">
-        <v>-1</v>
-      </c>
-      <c r="H13" s="5">
         <v>1</v>
       </c>
     </row>

--- a/table/resources/sample/RouletteShop.xlsx
+++ b/table/resources/sample/RouletteShop.xlsx
@@ -129,7 +129,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="23">
   <si>
     <t>id</t>
   </si>
@@ -179,22 +179,25 @@
     <t>open</t>
   </si>
   <si>
-    <t>1990000_3000</t>
+    <t>1990000_300000</t>
   </si>
   <si>
     <t>金币</t>
   </si>
   <si>
-    <t>1990000_2000</t>
-  </si>
-  <si>
-    <t>1990000_1300</t>
-  </si>
-  <si>
-    <t>1990000_650</t>
-  </si>
-  <si>
-    <t>1990000_100</t>
+    <t>1990000_200000</t>
+  </si>
+  <si>
+    <t>1990000_100000</t>
+  </si>
+  <si>
+    <t>1990000_50000</t>
+  </si>
+  <si>
+    <t>1990000_10000</t>
+  </si>
+  <si>
+    <t>1990000_500</t>
   </si>
 </sst>
 </file>
@@ -366,12 +369,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1160,7 +1163,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="3" max="3" width="10.5" customWidth="1"/>
@@ -1259,7 +1262,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="4">
-        <f>B5*1000+C5</f>
+        <f t="shared" ref="A5:A10" si="0">B5*1000+C5</f>
         <v>1001</v>
       </c>
       <c r="B5" s="4">
@@ -1275,8 +1278,7 @@
         <v>17</v>
       </c>
       <c r="F5" s="5">
-        <f t="shared" ref="F5:F9" si="0">N9</f>
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
@@ -1287,7 +1289,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="4">
-        <f>B6*1000+C6</f>
+        <f t="shared" si="0"/>
         <v>1002</v>
       </c>
       <c r="B6" s="4">
@@ -1303,8 +1305,7 @@
         <v>17</v>
       </c>
       <c r="F6" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
@@ -1315,7 +1316,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="4">
-        <f>B7*1000+C7</f>
+        <f t="shared" si="0"/>
         <v>1003</v>
       </c>
       <c r="B7" s="4">
@@ -1331,8 +1332,7 @@
         <v>17</v>
       </c>
       <c r="F7" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G7" s="5">
         <v>3</v>
@@ -1343,7 +1343,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="4">
-        <f>B8*1000+C8</f>
+        <f t="shared" si="0"/>
         <v>1004</v>
       </c>
       <c r="B8" s="4">
@@ -1359,8 +1359,7 @@
         <v>17</v>
       </c>
       <c r="F8" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="G8" s="5">
         <v>4</v>
@@ -1371,7 +1370,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="4">
-        <f>B9*1000+C9</f>
+        <f t="shared" si="0"/>
         <v>1005</v>
       </c>
       <c r="B9" s="4">
@@ -1387,13 +1386,39 @@
         <v>17</v>
       </c>
       <c r="F9" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G9" s="5">
         <v>5</v>
       </c>
       <c r="H9" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="4">
+        <f t="shared" si="0"/>
+        <v>1006</v>
+      </c>
+      <c r="B10" s="4">
+        <v>1</v>
+      </c>
+      <c r="C10" s="5">
+        <v>6</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="5">
+        <v>1000</v>
+      </c>
+      <c r="G10" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H10" s="5">
         <v>1</v>
       </c>
     </row>

--- a/table/resources/sample/RouletteShop.xlsx
+++ b/table/resources/sample/RouletteShop.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="RouletteShop" sheetId="1" r:id="rId1"/>
@@ -129,7 +129,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="23">
   <si>
     <t>id</t>
   </si>
@@ -179,58 +179,25 @@
     <t>open</t>
   </si>
   <si>
-    <t>1022501_5</t>
-  </si>
-  <si>
-    <t>祈福卡</t>
-  </si>
-  <si>
-    <t>1022502_1</t>
-  </si>
-  <si>
-    <t>刮刮卡</t>
-  </si>
-  <si>
-    <t>1022503_2</t>
-  </si>
-  <si>
-    <t>夺宝优惠券</t>
-  </si>
-  <si>
-    <t>1010301_1</t>
-  </si>
-  <si>
-    <t>赌场工具（普通）</t>
-  </si>
-  <si>
-    <t>1010302_1</t>
-  </si>
-  <si>
-    <t>赌场工具（精良）</t>
-  </si>
-  <si>
-    <t>1010303_1</t>
-  </si>
-  <si>
-    <t>赌场工具（优秀）</t>
-  </si>
-  <si>
-    <t>1010304_1</t>
-  </si>
-  <si>
-    <t>赌场工具（绝佳）</t>
-  </si>
-  <si>
-    <t>1010305_1</t>
-  </si>
-  <si>
-    <t>赌场工具（传奇）</t>
-  </si>
-  <si>
-    <t>1990000_30000</t>
+    <t>1990000_300000</t>
   </si>
   <si>
     <t>金币</t>
+  </si>
+  <si>
+    <t>1990000_200000</t>
+  </si>
+  <si>
+    <t>1990000_100000</t>
+  </si>
+  <si>
+    <t>1990000_50000</t>
+  </si>
+  <si>
+    <t>1990000_10000</t>
+  </si>
+  <si>
+    <t>1990000_500</t>
   </si>
 </sst>
 </file>
@@ -1196,7 +1163,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="3" max="3" width="10.5" customWidth="1"/>
@@ -1295,7 +1262,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="4">
-        <f>B5*1000+C5</f>
+        <f t="shared" ref="A5:A10" si="0">B5*1000+C5</f>
         <v>1001</v>
       </c>
       <c r="B5" s="4">
@@ -1307,14 +1274,14 @@
       <c r="D5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>17</v>
       </c>
       <c r="F5" s="5">
-        <v>5</v>
+        <v>300000</v>
       </c>
       <c r="G5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" s="5">
         <v>1</v>
@@ -1322,7 +1289,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="4">
-        <f t="shared" ref="A6:A13" si="0">B6*1000+C6</f>
+        <f t="shared" si="0"/>
         <v>1002</v>
       </c>
       <c r="B6" s="4">
@@ -1334,14 +1301,14 @@
       <c r="D6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>19</v>
+      <c r="E6" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="F6" s="5">
-        <v>60</v>
+        <v>200000</v>
       </c>
       <c r="G6" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" s="5">
         <v>1</v>
@@ -1359,16 +1326,16 @@
         <v>3</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="F7" s="5">
-        <v>100</v>
+        <v>100000</v>
       </c>
       <c r="G7" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H7" s="5">
         <v>1</v>
@@ -1386,16 +1353,16 @@
         <v>4</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="F8" s="5">
-        <v>10</v>
+        <v>50000</v>
       </c>
       <c r="G8" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H8" s="5">
         <v>1</v>
@@ -1413,13 +1380,13 @@
         <v>5</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F9" s="5">
-        <v>20</v>
+        <v>10000</v>
       </c>
       <c r="G9" s="5">
         <v>5</v>
@@ -1440,93 +1407,18 @@
         <v>6</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F10" s="5">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="G10" s="5">
-        <v>2</v>
-      </c>
-      <c r="H10" s="5"/>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="4">
-        <f t="shared" si="0"/>
-        <v>1007</v>
-      </c>
-      <c r="B11" s="4">
-        <v>1</v>
-      </c>
-      <c r="C11" s="5">
-        <v>7</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" s="5">
-        <v>80</v>
-      </c>
-      <c r="G11" s="5">
-        <v>1</v>
-      </c>
-      <c r="H11" s="5"/>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="4">
-        <f t="shared" si="0"/>
-        <v>1008</v>
-      </c>
-      <c r="B12" s="4">
-        <v>1</v>
-      </c>
-      <c r="C12" s="5">
-        <v>8</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="5">
-        <v>100</v>
-      </c>
-      <c r="G12" s="5">
-        <v>1</v>
-      </c>
-      <c r="H12" s="5"/>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="4">
-        <f t="shared" si="0"/>
-        <v>1009</v>
-      </c>
-      <c r="B13" s="4">
-        <v>1</v>
-      </c>
-      <c r="C13" s="5">
-        <v>9</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13" s="5">
-        <v>5</v>
-      </c>
-      <c r="G13" s="5">
         <v>-1</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H10" s="5">
         <v>1</v>
       </c>
     </row>

--- a/table/resources/sample/RouletteShop.xlsx
+++ b/table/resources/sample/RouletteShop.xlsx
@@ -1308,7 +1308,7 @@
         <v>200000</v>
       </c>
       <c r="G6" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" s="5">
         <v>1</v>
@@ -1335,7 +1335,7 @@
         <v>100000</v>
       </c>
       <c r="G7" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H7" s="5">
         <v>1</v>
@@ -1362,7 +1362,7 @@
         <v>50000</v>
       </c>
       <c r="G8" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H8" s="5">
         <v>1</v>
@@ -1389,7 +1389,7 @@
         <v>10000</v>
       </c>
       <c r="G9" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H9" s="5">
         <v>1</v>

--- a/table/resources/sample/RouletteShop.xlsx
+++ b/table/resources/sample/RouletteShop.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="RouletteShop" sheetId="1" r:id="rId1"/>
@@ -179,13 +179,13 @@
     <t>open</t>
   </si>
   <si>
-    <t>1990000_300000</t>
+    <t>1990000_800000</t>
   </si>
   <si>
     <t>金币</t>
   </si>
   <si>
-    <t>1990000_200000</t>
+    <t>1990000_400000</t>
   </si>
   <si>
     <t>1990000_100000</t>
@@ -197,7 +197,7 @@
     <t>1990000_10000</t>
   </si>
   <si>
-    <t>1990000_500</t>
+    <t>1990000_1000</t>
   </si>
 </sst>
 </file>
@@ -1262,7 +1262,6 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="4">
-        <f t="shared" ref="A5:A10" si="0">B5*1000+C5</f>
         <v>1001</v>
       </c>
       <c r="B5" s="4">
@@ -1278,7 +1277,7 @@
         <v>17</v>
       </c>
       <c r="F5" s="5">
-        <v>300000</v>
+        <v>800000</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
@@ -1289,7 +1288,6 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="4">
-        <f t="shared" si="0"/>
         <v>1002</v>
       </c>
       <c r="B6" s="4">
@@ -1305,7 +1303,7 @@
         <v>17</v>
       </c>
       <c r="F6" s="5">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="G6" s="5">
         <v>1</v>
@@ -1316,7 +1314,6 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="4">
-        <f t="shared" si="0"/>
         <v>1003</v>
       </c>
       <c r="B7" s="4">
@@ -1343,7 +1340,6 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="4">
-        <f t="shared" si="0"/>
         <v>1004</v>
       </c>
       <c r="B8" s="4">
@@ -1370,7 +1366,6 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="4">
-        <f t="shared" si="0"/>
         <v>1005</v>
       </c>
       <c r="B9" s="4">
@@ -1397,14 +1392,13 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="4">
-        <f t="shared" si="0"/>
         <v>1006</v>
       </c>
       <c r="B10" s="4">
         <v>1</v>
       </c>
       <c r="C10" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
@@ -1413,7 +1407,7 @@
         <v>17</v>
       </c>
       <c r="F10" s="5">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="G10" s="5">
         <v>-1</v>

--- a/table/resources/sample/RouletteShop.xlsx
+++ b/table/resources/sample/RouletteShop.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="RouletteShop" sheetId="1" r:id="rId1"/>
@@ -197,7 +197,7 @@
     <t>1990000_10000</t>
   </si>
   <si>
-    <t>1990000_1000</t>
+    <t>1990000_400</t>
   </si>
 </sst>
 </file>
@@ -369,12 +369,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1398,7 +1398,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>

--- a/table/resources/sample/RouletteShop.xlsx
+++ b/table/resources/sample/RouletteShop.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="RouletteShop" sheetId="1" r:id="rId1"/>
@@ -179,13 +179,13 @@
     <t>open</t>
   </si>
   <si>
-    <t>1990000_800000</t>
+    <t>1990000_300000</t>
   </si>
   <si>
     <t>金币</t>
   </si>
   <si>
-    <t>1990000_400000</t>
+    <t>1990000_200000</t>
   </si>
   <si>
     <t>1990000_100000</t>
@@ -197,7 +197,7 @@
     <t>1990000_10000</t>
   </si>
   <si>
-    <t>1990000_1000</t>
+    <t>1990000_500</t>
   </si>
 </sst>
 </file>
@@ -1262,6 +1262,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="4">
+        <f t="shared" ref="A5:A10" si="0">B5*1000+C5</f>
         <v>1001</v>
       </c>
       <c r="B5" s="4">
@@ -1277,7 +1278,7 @@
         <v>17</v>
       </c>
       <c r="F5" s="5">
-        <v>800000</v>
+        <v>300000</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
@@ -1288,6 +1289,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="4">
+        <f t="shared" si="0"/>
         <v>1002</v>
       </c>
       <c r="B6" s="4">
@@ -1303,7 +1305,7 @@
         <v>17</v>
       </c>
       <c r="F6" s="5">
-        <v>400000</v>
+        <v>200000</v>
       </c>
       <c r="G6" s="5">
         <v>1</v>
@@ -1314,6 +1316,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="4">
+        <f t="shared" si="0"/>
         <v>1003</v>
       </c>
       <c r="B7" s="4">
@@ -1340,6 +1343,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="4">
+        <f t="shared" si="0"/>
         <v>1004</v>
       </c>
       <c r="B8" s="4">
@@ -1366,6 +1370,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="4">
+        <f t="shared" si="0"/>
         <v>1005</v>
       </c>
       <c r="B9" s="4">
@@ -1392,13 +1397,14 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="4">
+        <f t="shared" si="0"/>
         <v>1006</v>
       </c>
       <c r="B10" s="4">
         <v>1</v>
       </c>
       <c r="C10" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
@@ -1407,7 +1413,7 @@
         <v>17</v>
       </c>
       <c r="F10" s="5">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="G10" s="5">
         <v>-1</v>

--- a/table/resources/sample/RouletteShop.xlsx
+++ b/table/resources/sample/RouletteShop.xlsx
@@ -179,13 +179,13 @@
     <t>open</t>
   </si>
   <si>
-    <t>1990000_300000</t>
+    <t>1990000_800000</t>
   </si>
   <si>
     <t>金币</t>
   </si>
   <si>
-    <t>1990000_200000</t>
+    <t>1990000_400000</t>
   </si>
   <si>
     <t>1990000_100000</t>
@@ -197,7 +197,7 @@
     <t>1990000_10000</t>
   </si>
   <si>
-    <t>1990000_500</t>
+    <t>1990000_400</t>
   </si>
 </sst>
 </file>
@@ -369,12 +369,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1262,7 +1262,6 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="4">
-        <f t="shared" ref="A5:A10" si="0">B5*1000+C5</f>
         <v>1001</v>
       </c>
       <c r="B5" s="4">
@@ -1278,7 +1277,7 @@
         <v>17</v>
       </c>
       <c r="F5" s="5">
-        <v>300000</v>
+        <v>800000</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
@@ -1289,7 +1288,6 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="4">
-        <f t="shared" si="0"/>
         <v>1002</v>
       </c>
       <c r="B6" s="4">
@@ -1305,7 +1303,7 @@
         <v>17</v>
       </c>
       <c r="F6" s="5">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="G6" s="5">
         <v>1</v>
@@ -1316,7 +1314,6 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="4">
-        <f t="shared" si="0"/>
         <v>1003</v>
       </c>
       <c r="B7" s="4">
@@ -1343,7 +1340,6 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="4">
-        <f t="shared" si="0"/>
         <v>1004</v>
       </c>
       <c r="B8" s="4">
@@ -1370,7 +1366,6 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="4">
-        <f t="shared" si="0"/>
         <v>1005</v>
       </c>
       <c r="B9" s="4">
@@ -1397,7 +1392,6 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="4">
-        <f t="shared" si="0"/>
         <v>1006</v>
       </c>
       <c r="B10" s="4">
@@ -1413,7 +1407,7 @@
         <v>17</v>
       </c>
       <c r="F10" s="5">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="G10" s="5">
         <v>-1</v>
